--- a/s10.xlsx
+++ b/s10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GAO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1D8F3-7CD7-4829-9933-40B52DF38B57}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5713D8A2-2F3C-489A-BA05-998FC36E93C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20955" windowHeight="7125" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20955" windowHeight="7125" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="星" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="510">
   <si>
     <t>首字母</t>
   </si>
@@ -2057,6 +2057,18 @@
   </si>
   <si>
     <t>真理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2380,7 +2392,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2538,9 +2550,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2838,549 +2847,549 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" style="54" customWidth="1"/>
-    <col min="2" max="3" width="9" style="54"/>
-    <col min="4" max="4" width="18.875" style="54" customWidth="1"/>
-    <col min="5" max="5" width="9" style="54"/>
-    <col min="6" max="6" width="19.375" style="54" customWidth="1"/>
-    <col min="7" max="8" width="9" style="54"/>
-    <col min="9" max="9" width="23.125" style="54" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="54" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="54"/>
+    <col min="1" max="1" width="19" style="53" customWidth="1"/>
+    <col min="2" max="3" width="9" style="53"/>
+    <col min="4" max="4" width="18.875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="9" style="53"/>
+    <col min="6" max="6" width="19.375" style="53" customWidth="1"/>
+    <col min="7" max="8" width="9" style="53"/>
+    <col min="9" max="9" width="23.125" style="53" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="53" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="J1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="K1" s="53" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="54">
+      <c r="B2" s="53">
         <v>6</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="53" t="s">
         <v>295</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="J2" s="54">
+      <c r="J2" s="53">
         <v>232</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="53" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="53">
         <v>6</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="53" t="s">
         <v>299</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="53" t="s">
         <v>300</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="53" t="s">
         <v>301</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="53" t="s">
         <v>302</v>
       </c>
-      <c r="G3" s="54" t="s">
+      <c r="G3" s="53" t="s">
         <v>299</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="53" t="s">
         <v>300</v>
       </c>
-      <c r="J3" s="54">
+      <c r="J3" s="53">
         <v>222</v>
       </c>
-      <c r="K3" s="54" t="s">
+      <c r="K3" s="53" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="53">
         <v>7</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>484</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="53" t="s">
         <v>486</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="53" t="s">
         <v>483</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="53" t="s">
         <v>485</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="53" t="s">
         <v>483</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="53" t="s">
         <v>478</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="53" t="s">
         <v>485</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="53">
         <v>511</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="53" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="53">
         <v>8</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="54" t="s">
+      <c r="I5" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="J5" s="54">
+      <c r="J5" s="53">
         <v>486</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="53" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="53">
         <v>8</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="53">
         <v>501</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="53" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="54">
+      <c r="B7" s="53">
         <v>8</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="G7" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="I7" s="54" t="s">
+      <c r="I7" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="53">
         <v>282</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="53" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="53">
         <v>9</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="53" t="s">
         <v>305</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="54" t="s">
+      <c r="I8" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="53">
         <v>597</v>
       </c>
-      <c r="K8" s="54" t="s">
+      <c r="K8" s="53" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="53">
         <v>6</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="54" t="s">
+      <c r="G9" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="J9" s="54">
+      <c r="J9" s="53">
         <v>251</v>
       </c>
-      <c r="K9" s="54" t="s">
+      <c r="K9" s="53" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="54">
+      <c r="B10" s="53">
         <v>6</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="53" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E10" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="54" t="s">
+      <c r="H10" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="54" t="s">
+      <c r="I10" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="53">
         <v>230</v>
       </c>
-      <c r="K10" s="54" t="s">
+      <c r="K10" s="53" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="53">
         <v>7</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="E11" s="54" t="s">
+      <c r="E11" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="F11" s="54" t="s">
+      <c r="F11" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="G11" s="54" t="s">
+      <c r="G11" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="54" t="s">
+      <c r="H11" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="54" t="s">
+      <c r="I11" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="53">
         <v>280</v>
       </c>
-      <c r="K11" s="54" t="s">
+      <c r="K11" s="53" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="53">
         <v>7</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="53" t="s">
         <v>309</v>
       </c>
-      <c r="E12" s="54" t="s">
+      <c r="E12" s="53" t="s">
         <v>310</v>
       </c>
-      <c r="F12" s="54" t="s">
+      <c r="F12" s="53" t="s">
         <v>311</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="53" t="s">
         <v>308</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="H12" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="I12" s="54" t="s">
+      <c r="I12" s="53" t="s">
         <v>312</v>
       </c>
-      <c r="J12" s="55">
+      <c r="J12" s="54">
         <v>298</v>
       </c>
-      <c r="K12" s="54" t="s">
+      <c r="K12" s="53" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="53">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="53">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="53">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="53">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="54">
+      <c r="B17" s="53">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="B18" s="54">
+      <c r="B18" s="53">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="B19" s="54">
+      <c r="B19" s="53">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="B20" s="54">
+      <c r="B20" s="53">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="53" t="s">
         <v>290</v>
       </c>
-      <c r="B21" s="54">
+      <c r="B21" s="53">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="55" t="s">
         <v>291</v>
       </c>
-      <c r="B22" s="54">
+      <c r="B22" s="53">
         <v>10</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="53" t="s">
         <v>476</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="53" t="s">
         <v>474</v>
       </c>
-      <c r="E22" s="54" t="s">
+      <c r="E22" s="53" t="s">
         <v>477</v>
       </c>
-      <c r="F22" s="54" t="s">
+      <c r="F22" s="53" t="s">
         <v>475</v>
       </c>
-      <c r="G22" s="54" t="s">
+      <c r="G22" s="53" t="s">
         <v>477</v>
       </c>
-      <c r="H22" s="54" t="s">
+      <c r="H22" s="53" t="s">
         <v>478</v>
       </c>
-      <c r="I22" s="54" t="s">
+      <c r="I22" s="53" t="s">
         <v>475</v>
       </c>
-      <c r="J22" s="54">
+      <c r="J22" s="53">
         <v>814</v>
       </c>
-      <c r="K22" s="54" t="s">
+      <c r="K22" s="53" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="53" t="s">
         <v>292</v>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="53">
         <v>10</v>
       </c>
     </row>
@@ -3438,10 +3447,13 @@
       <c r="D2" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="53">
         <v>232</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
+        <v>507</v>
+      </c>
+      <c r="G2" s="53" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3458,10 +3470,13 @@
       <c r="D3" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="53">
         <v>222</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" t="s">
+        <v>507</v>
+      </c>
+      <c r="G3" s="53" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3478,11 +3493,14 @@
       <c r="D4" s="23" t="s">
         <v>488</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="53">
         <v>511</v>
       </c>
-      <c r="G4" t="s">
-        <v>479</v>
+      <c r="F4" t="s">
+        <v>507</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -3498,6 +3516,15 @@
       <c r="D5" s="23" t="s">
         <v>234</v>
       </c>
+      <c r="E5" s="53">
+        <v>486</v>
+      </c>
+      <c r="F5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3512,6 +3539,15 @@
       <c r="D6" s="23" t="s">
         <v>236</v>
       </c>
+      <c r="E6" s="53">
+        <v>501</v>
+      </c>
+      <c r="F6" t="s">
+        <v>507</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -3526,6 +3562,15 @@
       <c r="D7" s="23" t="s">
         <v>238</v>
       </c>
+      <c r="E7" s="53">
+        <v>282</v>
+      </c>
+      <c r="F7" t="s">
+        <v>507</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3540,10 +3585,13 @@
       <c r="D8" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="53">
         <v>597</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F8" t="s">
+        <v>507</v>
+      </c>
+      <c r="G8" s="53" t="s">
         <v>307</v>
       </c>
     </row>
@@ -3560,6 +3608,15 @@
       <c r="D9" s="23" t="s">
         <v>208</v>
       </c>
+      <c r="E9" s="53">
+        <v>251</v>
+      </c>
+      <c r="F9" t="s">
+        <v>507</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3574,6 +3631,15 @@
       <c r="D10" s="23" t="s">
         <v>204</v>
       </c>
+      <c r="E10" s="53">
+        <v>230</v>
+      </c>
+      <c r="F10" t="s">
+        <v>507</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -3588,6 +3654,15 @@
       <c r="D11" s="23" t="s">
         <v>209</v>
       </c>
+      <c r="E11" s="53">
+        <v>280</v>
+      </c>
+      <c r="F11" t="s">
+        <v>507</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -3602,11 +3677,13 @@
       <c r="D12" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="54">
         <v>298</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" t="s">
+      <c r="F12" t="s">
+        <v>507</v>
+      </c>
+      <c r="G12" s="53" t="s">
         <v>313</v>
       </c>
     </row>
@@ -3716,6 +3793,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4293,6 +4371,9 @@
       <c r="E2">
         <v>228</v>
       </c>
+      <c r="F2" t="s">
+        <v>507</v>
+      </c>
       <c r="G2" t="s">
         <v>298</v>
       </c>
@@ -4313,6 +4394,9 @@
       <c r="E3">
         <v>204</v>
       </c>
+      <c r="F3" t="s">
+        <v>507</v>
+      </c>
       <c r="G3" t="s">
         <v>298</v>
       </c>
@@ -4333,6 +4417,9 @@
       <c r="E4">
         <v>477</v>
       </c>
+      <c r="F4" t="s">
+        <v>507</v>
+      </c>
       <c r="G4" t="s">
         <v>298</v>
       </c>
@@ -4350,6 +4437,15 @@
       <c r="D5" s="23" t="s">
         <v>279</v>
       </c>
+      <c r="E5" s="18">
+        <v>391</v>
+      </c>
+      <c r="F5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G5" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -4364,6 +4460,15 @@
       <c r="D6" s="23" t="s">
         <v>284</v>
       </c>
+      <c r="E6" s="18">
+        <v>391</v>
+      </c>
+      <c r="F6" t="s">
+        <v>507</v>
+      </c>
+      <c r="G6" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -4381,6 +4486,9 @@
       <c r="E7">
         <v>193</v>
       </c>
+      <c r="F7" t="s">
+        <v>507</v>
+      </c>
       <c r="G7" t="s">
         <v>298</v>
       </c>
@@ -4398,6 +4506,15 @@
       <c r="D8" s="23" t="s">
         <v>275</v>
       </c>
+      <c r="E8" s="18">
+        <v>429</v>
+      </c>
+      <c r="F8" t="s">
+        <v>507</v>
+      </c>
+      <c r="G8" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -4439,7 +4556,9 @@
       <c r="E12" s="46">
         <v>238</v>
       </c>
-      <c r="F12" s="46"/>
+      <c r="F12" s="46" t="s">
+        <v>507</v>
+      </c>
       <c r="G12" t="s">
         <v>313</v>
       </c>
@@ -4457,6 +4576,15 @@
       <c r="D13" s="23" t="s">
         <v>271</v>
       </c>
+      <c r="E13">
+        <v>398</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -4471,6 +4599,15 @@
       <c r="D14" s="23" t="s">
         <v>265</v>
       </c>
+      <c r="E14">
+        <v>490</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -4484,6 +4621,15 @@
       </c>
       <c r="D15" s="23" t="s">
         <v>180</v>
+      </c>
+      <c r="E15">
+        <v>334</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -5126,6 +5272,9 @@
       <c r="E2">
         <v>214</v>
       </c>
+      <c r="F2" s="23" t="s">
+        <v>507</v>
+      </c>
       <c r="G2" t="s">
         <v>90</v>
       </c>
@@ -5146,8 +5295,8 @@
       <c r="E3">
         <v>562</v>
       </c>
-      <c r="F3" s="46">
-        <v>998</v>
+      <c r="F3" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G3" t="s">
         <v>403</v>
@@ -5169,8 +5318,8 @@
       <c r="E4">
         <v>468</v>
       </c>
-      <c r="F4" s="46">
-        <v>816</v>
+      <c r="F4" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G4" t="s">
         <v>403</v>
@@ -5192,8 +5341,8 @@
       <c r="E5">
         <v>506</v>
       </c>
-      <c r="F5" s="46">
-        <v>1074</v>
+      <c r="F5" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G5" t="s">
         <v>403</v>
@@ -5215,8 +5364,8 @@
       <c r="E6">
         <v>229</v>
       </c>
-      <c r="F6" s="46">
-        <v>800</v>
+      <c r="F6" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G6" t="s">
         <v>403</v>
@@ -5238,8 +5387,8 @@
       <c r="E7">
         <v>545</v>
       </c>
-      <c r="F7">
-        <v>1278</v>
+      <c r="F7" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G7" t="s">
         <v>403</v>
@@ -5261,8 +5410,8 @@
       <c r="E8">
         <v>173</v>
       </c>
-      <c r="F8">
-        <v>351</v>
+      <c r="F8" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G8" t="s">
         <v>403</v>
@@ -5284,8 +5433,8 @@
       <c r="E9">
         <v>313</v>
       </c>
-      <c r="F9">
-        <v>586</v>
+      <c r="F9" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G9" t="s">
         <v>403</v>
@@ -5307,8 +5456,8 @@
       <c r="E10">
         <v>306</v>
       </c>
-      <c r="F10">
-        <v>602</v>
+      <c r="F10" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G10" t="s">
         <v>403</v>
@@ -5330,8 +5479,8 @@
       <c r="E11">
         <v>559</v>
       </c>
-      <c r="F11">
-        <v>1203</v>
+      <c r="F11" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G11" t="s">
         <v>364</v>
@@ -5353,8 +5502,8 @@
       <c r="E12">
         <v>599</v>
       </c>
-      <c r="F12">
-        <v>1239</v>
+      <c r="F12" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G12" t="s">
         <v>364</v>
@@ -5376,8 +5525,8 @@
       <c r="E13">
         <v>394</v>
       </c>
-      <c r="F13" s="52">
-        <v>897</v>
+      <c r="F13" s="23" t="s">
+        <v>507</v>
       </c>
       <c r="G13" t="s">
         <v>364</v>
@@ -6684,6 +6833,9 @@
       <c r="E2" s="28">
         <v>184</v>
       </c>
+      <c r="F2" t="s">
+        <v>507</v>
+      </c>
       <c r="G2" s="33" t="s">
         <v>90</v>
       </c>
@@ -6704,6 +6856,9 @@
       <c r="E3" s="14">
         <v>175</v>
       </c>
+      <c r="F3" t="s">
+        <v>507</v>
+      </c>
       <c r="G3" s="35" t="s">
         <v>90</v>
       </c>
@@ -6724,6 +6879,9 @@
       <c r="E4" s="7">
         <v>233</v>
       </c>
+      <c r="F4" t="s">
+        <v>507</v>
+      </c>
       <c r="G4" s="48" t="s">
         <v>307</v>
       </c>
@@ -6744,6 +6902,9 @@
       <c r="E5" s="49">
         <v>311</v>
       </c>
+      <c r="F5" t="s">
+        <v>507</v>
+      </c>
       <c r="G5" s="48" t="s">
         <v>364</v>
       </c>
@@ -6764,6 +6925,9 @@
       <c r="E6" s="51">
         <v>305</v>
       </c>
+      <c r="F6" t="s">
+        <v>507</v>
+      </c>
       <c r="G6" s="48" t="s">
         <v>364</v>
       </c>
@@ -6784,6 +6948,9 @@
       <c r="E7" s="49">
         <v>423</v>
       </c>
+      <c r="F7" t="s">
+        <v>507</v>
+      </c>
       <c r="G7" s="48" t="s">
         <v>307</v>
       </c>
@@ -6804,6 +6971,9 @@
       <c r="E8" s="14">
         <v>266</v>
       </c>
+      <c r="F8" t="s">
+        <v>507</v>
+      </c>
       <c r="G8" s="35" t="s">
         <v>135</v>
       </c>
@@ -6824,6 +6994,9 @@
       <c r="E9" s="14">
         <v>179</v>
       </c>
+      <c r="F9" t="s">
+        <v>507</v>
+      </c>
       <c r="G9" s="35" t="s">
         <v>90</v>
       </c>
@@ -6844,6 +7017,9 @@
       <c r="E10" s="19">
         <v>144</v>
       </c>
+      <c r="F10" t="s">
+        <v>507</v>
+      </c>
       <c r="G10" s="19" t="s">
         <v>78</v>
       </c>
@@ -6864,6 +7040,9 @@
       <c r="E11" s="14">
         <v>191</v>
       </c>
+      <c r="F11" t="s">
+        <v>507</v>
+      </c>
       <c r="G11" s="35" t="s">
         <v>90</v>
       </c>
@@ -6884,6 +7063,9 @@
       <c r="E12" s="14">
         <v>223</v>
       </c>
+      <c r="F12" t="s">
+        <v>507</v>
+      </c>
       <c r="G12" s="35" t="s">
         <v>90</v>
       </c>
@@ -6904,6 +7086,9 @@
       <c r="E13" s="14">
         <v>197</v>
       </c>
+      <c r="F13" t="s">
+        <v>507</v>
+      </c>
       <c r="G13" s="35" t="s">
         <v>135</v>
       </c>
@@ -6924,6 +7109,9 @@
       <c r="E14" s="14">
         <v>188</v>
       </c>
+      <c r="F14" t="s">
+        <v>507</v>
+      </c>
       <c r="G14" s="35" t="s">
         <v>135</v>
       </c>
@@ -6944,6 +7132,9 @@
       <c r="E15" s="14">
         <v>135</v>
       </c>
+      <c r="F15" t="s">
+        <v>507</v>
+      </c>
       <c r="G15" s="35" t="s">
         <v>90</v>
       </c>
@@ -6964,6 +7155,9 @@
       <c r="E16" s="14">
         <v>171</v>
       </c>
+      <c r="F16" t="s">
+        <v>507</v>
+      </c>
       <c r="G16" s="35" t="s">
         <v>90</v>
       </c>
@@ -6976,6 +7170,9 @@
         <v>36</v>
       </c>
       <c r="E17" s="34"/>
+      <c r="F17" t="s">
+        <v>507</v>
+      </c>
       <c r="G17" s="35"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.2">
@@ -6994,6 +7191,9 @@
       <c r="E18" s="14">
         <v>121</v>
       </c>
+      <c r="F18" t="s">
+        <v>507</v>
+      </c>
       <c r="G18" s="35" t="s">
         <v>135</v>
       </c>
@@ -7014,6 +7214,9 @@
       <c r="E19" s="14">
         <v>196</v>
       </c>
+      <c r="F19" t="s">
+        <v>507</v>
+      </c>
       <c r="G19" s="48" t="s">
         <v>307</v>
       </c>
@@ -7034,6 +7237,9 @@
       <c r="E20" s="14">
         <v>252</v>
       </c>
+      <c r="F20" t="s">
+        <v>507</v>
+      </c>
       <c r="G20" s="48" t="s">
         <v>307</v>
       </c>
@@ -7054,6 +7260,9 @@
       <c r="E21" s="14">
         <v>195</v>
       </c>
+      <c r="F21" t="s">
+        <v>507</v>
+      </c>
       <c r="G21" s="35" t="s">
         <v>135</v>
       </c>
@@ -7074,6 +7283,9 @@
       <c r="E22" s="14">
         <v>180</v>
       </c>
+      <c r="F22" t="s">
+        <v>507</v>
+      </c>
       <c r="G22" s="35" t="s">
         <v>135</v>
       </c>
@@ -7094,6 +7306,9 @@
       <c r="E23" s="49">
         <v>257</v>
       </c>
+      <c r="F23" t="s">
+        <v>507</v>
+      </c>
       <c r="G23" s="48" t="s">
         <v>307</v>
       </c>
@@ -7102,7 +7317,7 @@
       <c r="A24" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="52" t="s">
         <v>438</v>
       </c>
       <c r="C24" t="s">
@@ -7113,6 +7328,9 @@
       </c>
       <c r="E24" s="49">
         <v>220</v>
+      </c>
+      <c r="F24" t="s">
+        <v>507</v>
       </c>
       <c r="G24" s="48" t="s">
         <v>364</v>
@@ -7134,6 +7352,9 @@
       <c r="E25" s="14">
         <v>96</v>
       </c>
+      <c r="F25" t="s">
+        <v>507</v>
+      </c>
       <c r="G25" s="35" t="s">
         <v>135</v>
       </c>
@@ -7154,6 +7375,9 @@
       <c r="E26" s="14">
         <v>242</v>
       </c>
+      <c r="F26" t="s">
+        <v>507</v>
+      </c>
       <c r="G26" s="35" t="s">
         <v>135</v>
       </c>
@@ -7174,6 +7398,9 @@
       <c r="E27" s="14">
         <v>287</v>
       </c>
+      <c r="F27" t="s">
+        <v>507</v>
+      </c>
       <c r="G27" s="48" t="s">
         <v>364</v>
       </c>
@@ -7194,6 +7421,9 @@
       <c r="E28" s="14">
         <v>143</v>
       </c>
+      <c r="F28" t="s">
+        <v>507</v>
+      </c>
       <c r="G28" s="35" t="s">
         <v>90</v>
       </c>
@@ -7214,6 +7444,9 @@
       <c r="E29" s="49">
         <v>199</v>
       </c>
+      <c r="F29" t="s">
+        <v>507</v>
+      </c>
       <c r="G29" s="48" t="s">
         <v>364</v>
       </c>
@@ -7234,12 +7467,17 @@
       <c r="E30" s="14">
         <v>183</v>
       </c>
+      <c r="F30" t="s">
+        <v>507</v>
+      </c>
       <c r="G30" s="35" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
+      <c r="A31" s="23" t="s">
+        <v>509</v>
+      </c>
       <c r="B31" s="17" t="s">
         <v>67</v>
       </c>
@@ -7251,6 +7489,9 @@
       </c>
       <c r="E31" s="23">
         <v>222</v>
+      </c>
+      <c r="F31" t="s">
+        <v>507</v>
       </c>
       <c r="G31" s="23" t="s">
         <v>135</v>

--- a/s10.xlsx
+++ b/s10.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20366"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\py_xw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCEB9D2-BE12-43EF-9C85-BE8F520FDD26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20955" windowHeight="7125" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20955" windowHeight="7125" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="星" sheetId="1" r:id="rId1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="784">
   <si>
     <t>首字母</t>
   </si>
@@ -2630,11 +2631,499 @@
 E：二轨条</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>A152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：滑球后让两个单点爆左单点
+E：双压</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B690</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：小空白后爆第二个单点（左）
+E：左单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B688</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左白球
+E：双条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B429</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左单条后爆白球
+E：左白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：681左直条按住2cb
+E：左白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A261</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：左直条后爆右单点
+E：双条结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：右手滑球后左直条
+E：左滑+右点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B757</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左点+右条后让左二连点爆右二连点
+E：右单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B728</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左条后爆右点后右条
+E：左二连点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A138</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：一轨单点
+E：二轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B324</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：四轨单点
+E：二轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：二轨二连点
+E：三轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B598</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：594右手直条按住3cb
+E：左白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左直条按住1cb
+E：右滑球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B620</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左直条后右手单点
+E：右手白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B356</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左白球
+E：左二连点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：左白球
+E：左二连点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B348</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：右二连点
+E：左二连点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：右单点后左单点（压）
+E：右白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A74</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：左手白球
+E：右手白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A96</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：左手二连点
+E：右手二连点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A148</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：双打后，过小空白爆第二个单点（三轨）（压）
+E：四轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：双打后，过小空白爆第二个单点（二轨）（压）
+E：一轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B836</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：2-1滑键后爆一轨条+4-3滑键
+E：双长条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：左直条后右手白球（存）
+E：左单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：右滑球后左单点
+E：左白球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：125右直条按住2cb
+E：右手二连点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B516</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：二轨拐条左滑
+E：2-1滑键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：一轨拐条右滑
+E：四轨拐条左滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B433</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：一轨直条按住1cb
+E：一轨直条右滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A332</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：二轨直条按住1cb
+E：一轨条右滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：三轨直条按住2cb
+E：四轨直条左滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A388</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：二三轨双拐
+E：二轨条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B772</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：一轨单点
+E：一轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B659</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：653四轨直条按住5cb
+E：4-3滑键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B744</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：一轨条按住1cb
+E：三轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：一轨单点
+E：三轨单点（压）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：三轨单点
+E：二轨直条头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：三轨直条按住
+E：四轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B419</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：二轨条
+E：四轨条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B567</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：三轨条右滑
+E：二轨条左滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B536</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：二轨条左滑
+E：二轨条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A384</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：第三组双点
+E：双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1276</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：第三组双点
+E：双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：第三组双点
+E：左滑点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A362</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：左滑点后爆右单点（存）
+E：左单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B689</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左滑条后右单点
+E：右滑点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B591</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：583右滑条按住7cb
+E：左单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：右滑条按住
+E：左滑点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心上人呀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invader</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEAD OR LIE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：B开过一组密集乱点后，爆3-4滑键后的第一个四轨单点
+E：三轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：631左手2-1拐条后，爆第四个二轨单点
+E：一轨+四轨双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B659</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B584</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：B开过一组密集乱点后，爆3-4滑键、2-1滑键后的第一个单点（三轨）
+E：三轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2984,7 +3473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3200,10 +3689,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3480,8 +3975,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" style="48" customWidth="1"/>
@@ -3879,21 +4374,37 @@
         <v>298</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="56" t="s">
         <v>441</v>
       </c>
       <c r="B13" s="56">
         <v>9</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
+      <c r="C13" s="48" t="s">
+        <v>717</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>733</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>731</v>
+      </c>
+      <c r="F13" s="56" t="s">
+        <v>732</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>731</v>
+      </c>
+      <c r="H13" s="56" t="s">
+        <v>679</v>
+      </c>
+      <c r="I13" s="56" t="s">
+        <v>732</v>
+      </c>
+      <c r="J13" s="56">
+        <v>410</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A14" s="56" t="s">
@@ -3959,12 +4470,36 @@
         <v>410</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="56" t="s">
         <v>453</v>
       </c>
       <c r="B16" s="56">
         <v>6</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>694</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>695</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>696</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>697</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>694</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>698</v>
+      </c>
+      <c r="I16" s="48" t="s">
+        <v>695</v>
+      </c>
+      <c r="J16" s="48">
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
@@ -4191,37 +4726,69 @@
         <v>750</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="56" t="s">
         <v>484</v>
       </c>
       <c r="B24" s="56">
         <v>6</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="56"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C24" s="56" t="s">
+        <v>754</v>
+      </c>
+      <c r="D24" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>756</v>
+      </c>
+      <c r="F24" s="48" t="s">
+        <v>757</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>754</v>
+      </c>
+      <c r="H24" s="56" t="s">
+        <v>698</v>
+      </c>
+      <c r="I24" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="J24" s="56">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A25" s="56" t="s">
         <v>485</v>
       </c>
       <c r="B25" s="56">
         <v>6</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
+      <c r="C25" s="56" t="s">
+        <v>744</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>745</v>
+      </c>
+      <c r="E25" s="56" t="s">
+        <v>742</v>
+      </c>
+      <c r="F25" s="56" t="s">
+        <v>743</v>
+      </c>
+      <c r="G25" s="56" t="s">
+        <v>742</v>
+      </c>
+      <c r="H25" s="56" t="s">
+        <v>679</v>
+      </c>
+      <c r="I25" s="56" t="s">
+        <v>743</v>
+      </c>
+      <c r="J25" s="56">
+        <v>372</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="56" t="s">
@@ -4255,69 +4822,165 @@
         <v>408</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="56" t="s">
         <v>491</v>
       </c>
       <c r="B27" s="56">
         <v>7</v>
       </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-    </row>
-    <row r="28" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C27" s="48" t="s">
+        <v>750</v>
+      </c>
+      <c r="D27" s="48" t="s">
+        <v>751</v>
+      </c>
+      <c r="E27" s="56" t="s">
+        <v>748</v>
+      </c>
+      <c r="F27" s="56" t="s">
+        <v>749</v>
+      </c>
+      <c r="G27" s="56" t="s">
+        <v>748</v>
+      </c>
+      <c r="H27" s="56" t="s">
+        <v>698</v>
+      </c>
+      <c r="I27" s="56" t="s">
+        <v>749</v>
+      </c>
+      <c r="J27" s="56">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A28" s="56" t="s">
         <v>492</v>
       </c>
       <c r="B28" s="56">
         <v>8</v>
       </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C28" s="48" t="s">
+        <v>720</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>721</v>
+      </c>
+      <c r="E28" s="56" t="s">
+        <v>719</v>
+      </c>
+      <c r="F28" s="56" t="s">
+        <v>722</v>
+      </c>
+      <c r="G28" s="56" t="s">
+        <v>719</v>
+      </c>
+      <c r="H28" s="56" t="s">
+        <v>679</v>
+      </c>
+      <c r="I28" s="56" t="s">
+        <v>722</v>
+      </c>
+      <c r="J28" s="56">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="56" t="s">
         <v>493</v>
       </c>
       <c r="B29" s="56">
         <v>8</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
+      <c r="C29" s="56" t="s">
+        <v>736</v>
+      </c>
+      <c r="D29" s="56" t="s">
+        <v>737</v>
+      </c>
+      <c r="E29" s="56" t="s">
+        <v>738</v>
+      </c>
+      <c r="F29" s="56" t="s">
+        <v>739</v>
+      </c>
+      <c r="G29" s="56" t="s">
+        <v>736</v>
+      </c>
+      <c r="H29" s="56" t="s">
+        <v>679</v>
+      </c>
+      <c r="I29" s="56" t="s">
+        <v>737</v>
+      </c>
+      <c r="J29" s="56">
+        <v>623</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
         <v>494</v>
       </c>
-      <c r="B30" s="56">
+      <c r="B30" s="48">
         <v>10</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="48" t="s">
+        <v>773</v>
+      </c>
+      <c r="B31" s="48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="48" t="s">
+        <v>774</v>
+      </c>
+      <c r="B32" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="57" x14ac:dyDescent="0.2">
+      <c r="A33" s="48" t="s">
+        <v>775</v>
+      </c>
+      <c r="B33" s="48">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>777</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>778</v>
+      </c>
+      <c r="E33" t="s">
+        <v>781</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>779</v>
+      </c>
+      <c r="G33" t="s">
+        <v>781</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>780</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>779</v>
+      </c>
+      <c r="J33">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="48" t="s">
+        <v>776</v>
+      </c>
+      <c r="B34" s="48">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4327,8 +4990,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.375" customWidth="1"/>
@@ -4588,12 +5251,18 @@
       </c>
       <c r="G12" s="48"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>441</v>
       </c>
       <c r="B13" s="59">
         <v>9</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -4636,12 +5305,18 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>453</v>
       </c>
       <c r="B16" s="59">
         <v>6</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>699</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -4775,20 +5450,32 @@
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="48" t="s">
         <v>484</v>
       </c>
       <c r="B24" s="48">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C24" s="23" t="s">
+        <v>758</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="48" t="s">
         <v>485</v>
       </c>
       <c r="B25" s="48">
         <v>6</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>746</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -4811,28 +5498,46 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
         <v>491</v>
       </c>
       <c r="B27" s="48">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C27" s="23" t="s">
+        <v>752</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="48" t="s">
         <v>492</v>
       </c>
       <c r="B28" s="48">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>723</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
         <v>493</v>
       </c>
       <c r="B29" s="48">
         <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>740</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
@@ -4840,6 +5545,44 @@
         <v>494</v>
       </c>
       <c r="B30" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="48" t="s">
+        <v>773</v>
+      </c>
+      <c r="B31" s="48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="48" t="s">
+        <v>774</v>
+      </c>
+      <c r="B32" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="48" t="s">
+        <v>775</v>
+      </c>
+      <c r="B33" s="48">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>782</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="48" t="s">
+        <v>776</v>
+      </c>
+      <c r="B34" s="48">
         <v>10</v>
       </c>
     </row>
@@ -4851,8 +5594,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -5120,12 +5863,36 @@
       </c>
       <c r="K8" s="18"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>425</v>
       </c>
       <c r="B9" s="59">
         <v>6</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>709</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>710</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>707</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>707</v>
+      </c>
+      <c r="H9" s="71" t="s">
+        <v>698</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="J9" s="18">
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -5136,12 +5903,36 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>435</v>
       </c>
       <c r="B11" s="59">
         <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>725</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>726</v>
+      </c>
+      <c r="E11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>728</v>
+      </c>
+      <c r="G11" t="s">
+        <v>727</v>
+      </c>
+      <c r="H11" t="s">
+        <v>698</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>728</v>
+      </c>
+      <c r="J11">
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
@@ -5563,48 +6354,195 @@
         <v>314</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A25" s="58" t="s">
         <v>486</v>
       </c>
       <c r="B25" s="48">
         <v>7</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C25" s="23" t="s">
+        <v>701</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>702</v>
+      </c>
+      <c r="E25" t="s">
+        <v>703</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>704</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>701</v>
+      </c>
+      <c r="H25" s="71" t="s">
+        <v>679</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>702</v>
+      </c>
+      <c r="J25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
         <v>491</v>
       </c>
       <c r="B26" s="48">
         <v>7</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-    </row>
-    <row r="27" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C26" s="23" t="s">
+        <v>715</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>716</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>713</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>714</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>713</v>
+      </c>
+      <c r="H26" s="71" t="s">
+        <v>698</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>714</v>
+      </c>
+      <c r="J26">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
         <v>492</v>
       </c>
       <c r="B27" s="48">
         <v>8</v>
       </c>
-      <c r="C27" s="23"/>
-    </row>
-    <row r="28" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C27" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="E27" t="s">
+        <v>677</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="J27">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="57" t="s">
         <v>493</v>
       </c>
       <c r="B28" s="48">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C28" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="E28" t="s">
+        <v>684</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="J28">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
         <v>494</v>
       </c>
       <c r="B29" s="48">
+        <v>10</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="E29" t="s">
+        <v>690</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>691</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="J29">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="48" t="s">
+        <v>773</v>
+      </c>
+      <c r="B30" s="48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="48" t="s">
+        <v>774</v>
+      </c>
+      <c r="B31" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="48" t="s">
+        <v>775</v>
+      </c>
+      <c r="B32" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="48" t="s">
+        <v>776</v>
+      </c>
+      <c r="B33" s="48">
         <v>10</v>
       </c>
     </row>
@@ -5616,8 +6554,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -5784,14 +6722,19 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>425</v>
       </c>
       <c r="B9" s="59">
         <v>6</v>
       </c>
-      <c r="C9" s="65"/>
+      <c r="C9" s="65" t="s">
+        <v>711</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>712</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -5802,14 +6745,19 @@
       </c>
       <c r="C10" s="65"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>435</v>
       </c>
       <c r="B11" s="59">
         <v>6</v>
       </c>
-      <c r="C11" s="65"/>
+      <c r="C11" s="65" t="s">
+        <v>729</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>730</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -6083,50 +7031,107 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="58" t="s">
         <v>486</v>
       </c>
       <c r="B25" s="48">
         <v>7</v>
       </c>
-      <c r="C25" s="23"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="23" t="s">
+        <v>705</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
         <v>491</v>
       </c>
       <c r="B26" s="48">
         <v>7</v>
       </c>
-      <c r="C26" s="23"/>
-    </row>
-    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C26" s="23" t="s">
+        <v>717</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
         <v>492</v>
       </c>
       <c r="B27" s="48">
         <v>8</v>
       </c>
-      <c r="C27" s="23"/>
-    </row>
-    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C27" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="57" t="s">
         <v>493</v>
       </c>
       <c r="B28" s="48">
         <v>8</v>
       </c>
-      <c r="C28" s="65"/>
-    </row>
-    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C28" s="65" t="s">
+        <v>686</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
         <v>494</v>
       </c>
       <c r="B29" s="48">
         <v>10</v>
       </c>
-      <c r="C29" s="65"/>
+      <c r="C29" s="65" t="s">
+        <v>692</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="48" t="s">
+        <v>773</v>
+      </c>
+      <c r="B30" s="48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="48" t="s">
+        <v>774</v>
+      </c>
+      <c r="B31" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="48" t="s">
+        <v>775</v>
+      </c>
+      <c r="B32" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="48" t="s">
+        <v>776</v>
+      </c>
+      <c r="B33" s="48">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6135,8 +7140,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -6722,23 +7727,69 @@
         <v>654</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="65" t="s">
         <v>478</v>
       </c>
       <c r="B19" s="59">
         <v>10</v>
       </c>
-      <c r="H19" s="23"/>
-    </row>
-    <row r="20" spans="1:10" ht="33" x14ac:dyDescent="0.2">
+      <c r="C19" s="61" t="s">
+        <v>760</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>761</v>
+      </c>
+      <c r="E19" t="s">
+        <v>762</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>763</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>760</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>761</v>
+      </c>
+      <c r="J19" s="72">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="69" t="s">
         <v>486</v>
       </c>
       <c r="B20" s="48">
         <v>6</v>
       </c>
-      <c r="H20" s="23"/>
+      <c r="C20" s="61" t="s">
+        <v>765</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>766</v>
+      </c>
+      <c r="E20" t="s">
+        <v>769</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>770</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>771</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>772</v>
+      </c>
+      <c r="J20" s="72">
+        <v>401</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A21" s="56" t="s">
@@ -6769,7 +7820,7 @@
         <v>634</v>
       </c>
       <c r="J21">
-        <v>466</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
@@ -6848,15 +7899,40 @@
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
     </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="48" t="s">
+        <v>774</v>
+      </c>
+      <c r="B25" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="48" t="s">
+        <v>775</v>
+      </c>
+      <c r="B26" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="48" t="s">
+        <v>776</v>
+      </c>
+      <c r="B27" s="48">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.25" style="23" customWidth="1"/>
@@ -7238,23 +8314,35 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>478</v>
       </c>
       <c r="B19" s="59">
         <v>10</v>
       </c>
+      <c r="C19" s="61" t="s">
+        <v>760</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>764</v>
+      </c>
       <c r="F19" s="53" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="58" t="s">
         <v>486</v>
       </c>
       <c r="B20" s="48">
         <v>6</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>767</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>768</v>
       </c>
       <c r="F20" s="53" t="s">
         <v>186</v>
@@ -7274,7 +8362,7 @@
         <v>647</v>
       </c>
       <c r="E21" s="23">
-        <v>466</v>
+        <v>224</v>
       </c>
       <c r="F21" s="53" t="s">
         <v>186</v>
@@ -7326,6 +8414,30 @@
       </c>
       <c r="F24" s="53" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="48" t="s">
+        <v>774</v>
+      </c>
+      <c r="B25" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="48" t="s">
+        <v>775</v>
+      </c>
+      <c r="B26" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="48" t="s">
+        <v>776</v>
+      </c>
+      <c r="B27" s="48">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7335,7 +8447,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -8480,7 +9592,7 @@
     <row r="40" customFormat="1" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="41" customFormat="1" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:M41">
+  <autoFilter ref="A1:M41" xr:uid="{00000000-0009-0000-0000-000006000000}">
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8494,7 +9606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>

--- a/s10.xlsx
+++ b/s10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCEB9D2-BE12-43EF-9C85-BE8F520FDD26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428F24C3-BDA0-4F42-8190-706E105B2777}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20955" windowHeight="7125" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20955" windowHeight="7125" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="星" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="799">
   <si>
     <t>首字母</t>
   </si>
@@ -1548,9 +1548,6 @@
   <si>
     <t>A：双打后,按着左条爆右滑球
 E：双打</t>
-  </si>
-  <si>
-    <t>花戏</t>
   </si>
   <si>
     <t>B714</t>
@@ -1854,15 +1851,8 @@
     <t>天秤</t>
   </si>
   <si>
-    <t>A647</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>A：按着1轨条+3轨滑键，立马爆
 E：4轨弯最后一拐</t>
-  </si>
-  <si>
-    <t>B1451</t>
   </si>
   <si>
     <t>B：按着4轨条+2轨滑键，立马爆
@@ -2034,9 +2024,6 @@
 E：一三轨双点</t>
   </si>
   <si>
-    <t>B1139</t>
-  </si>
-  <si>
     <t>B：按着2轨条，即将一拐时爆
 E：阶梯点+右滑键结束</t>
   </si>
@@ -3117,6 +3104,90 @@
   <si>
     <t>B：B开过一组密集乱点后，爆3-4滑键、2-1滑键后的第一个单点（三轨）
 E：三轨单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：584左手滑点后过两个单点爆左手单点（存）
+E：双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B868</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：右、左滑点后，过双点爆左手单点+右手滑条
+E：左手滑点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：右、左滑点后，过双点爆左手单点+右手滑条
+E：双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B854</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：左手滑点后，左手直条+右手单点按住5cb爆
+E：双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A474</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：468双点后过右手两单点和左手滑球爆左手单点
+E：双点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：1097左直条后，过右手单点、右手白球、左手单点后爆双点
+E：左手直条+右手单点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B：1043左手直条+右手单点后，过右手二单点爆双点
+E：左手直条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A649</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>A：按着1轨条+3轨滑键，立马爆
+E：4轨弯最后一拐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1453</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极限</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3992,7 +4063,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="56" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B1" s="56" t="s">
         <v>1</v>
@@ -4024,7 +4095,7 @@
     </row>
     <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" s="56" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="56">
         <v>6</v>
@@ -4056,7 +4127,7 @@
     </row>
     <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B3" s="56">
         <v>6</v>
@@ -4088,31 +4159,31 @@
     </row>
     <row r="4" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" s="56" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" s="56">
         <v>7</v>
       </c>
       <c r="C4" s="56" t="s">
+        <v>403</v>
+      </c>
+      <c r="D4" s="56" t="s">
         <v>404</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="E4" s="56" t="s">
         <v>405</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="F4" s="56" t="s">
         <v>406</v>
       </c>
-      <c r="F4" s="56" t="s">
-        <v>407</v>
-      </c>
       <c r="G4" s="56" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>64</v>
       </c>
       <c r="I4" s="56" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J4" s="56">
         <v>511</v>
@@ -4120,31 +4191,31 @@
     </row>
     <row r="5" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="56" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B5" s="56">
         <v>8</v>
       </c>
       <c r="C5" s="56" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" s="56" t="s">
         <v>409</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="E5" s="56" t="s">
         <v>410</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="F5" s="56" t="s">
         <v>411</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="G5" s="56" t="s">
         <v>412</v>
-      </c>
-      <c r="G5" s="56" t="s">
-        <v>413</v>
       </c>
       <c r="H5" s="56" t="s">
         <v>64</v>
       </c>
       <c r="I5" s="56" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J5" s="56">
         <v>486</v>
@@ -4152,31 +4223,31 @@
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B6" s="56">
         <v>8</v>
       </c>
       <c r="C6" s="56" t="s">
+        <v>415</v>
+      </c>
+      <c r="D6" s="56" t="s">
         <v>416</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="E6" s="56" t="s">
         <v>417</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="F6" s="56" t="s">
         <v>418</v>
       </c>
-      <c r="F6" s="56" t="s">
-        <v>419</v>
-      </c>
       <c r="G6" s="56" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H6" s="56" t="s">
         <v>64</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J6" s="56">
         <v>501</v>
@@ -4184,7 +4255,7 @@
     </row>
     <row r="7" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="56" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" s="56">
         <v>8</v>
@@ -4193,13 +4264,13 @@
         <v>322</v>
       </c>
       <c r="D7" s="56" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" s="56" t="s">
         <v>421</v>
       </c>
-      <c r="E7" s="56" t="s">
+      <c r="F7" s="56" t="s">
         <v>422</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>423</v>
       </c>
       <c r="G7" s="56" t="s">
         <v>322</v>
@@ -4208,7 +4279,7 @@
         <v>64</v>
       </c>
       <c r="I7" s="56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J7" s="56">
         <v>282</v>
@@ -4216,7 +4287,7 @@
     </row>
     <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="56" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B8" s="56">
         <v>9</v>
@@ -4248,31 +4319,31 @@
     </row>
     <row r="9" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="56" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B9" s="56">
         <v>6</v>
       </c>
       <c r="C9" s="56" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" s="56" t="s">
         <v>426</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="E9" s="56" t="s">
         <v>427</v>
       </c>
-      <c r="E9" s="56" t="s">
+      <c r="F9" s="56" t="s">
         <v>428</v>
       </c>
-      <c r="F9" s="56" t="s">
-        <v>429</v>
-      </c>
       <c r="G9" s="56" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H9" s="56" t="s">
         <v>186</v>
       </c>
       <c r="I9" s="56" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J9" s="56">
         <v>251</v>
@@ -4280,31 +4351,31 @@
     </row>
     <row r="10" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="56" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B10" s="56">
         <v>6</v>
       </c>
       <c r="C10" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="D10" s="56" t="s">
         <v>431</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="E10" s="56" t="s">
         <v>432</v>
       </c>
-      <c r="E10" s="56" t="s">
+      <c r="F10" s="56" t="s">
         <v>433</v>
       </c>
-      <c r="F10" s="56" t="s">
-        <v>434</v>
-      </c>
       <c r="G10" s="56" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H10" s="56" t="s">
         <v>186</v>
       </c>
       <c r="I10" s="56" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J10" s="56">
         <v>230</v>
@@ -4312,31 +4383,31 @@
     </row>
     <row r="11" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" s="56" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B11" s="56">
         <v>7</v>
       </c>
       <c r="C11" s="56" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11" s="56" t="s">
         <v>436</v>
       </c>
-      <c r="D11" s="56" t="s">
+      <c r="E11" s="56" t="s">
         <v>437</v>
       </c>
-      <c r="E11" s="56" t="s">
+      <c r="F11" s="56" t="s">
         <v>438</v>
       </c>
-      <c r="F11" s="56" t="s">
-        <v>439</v>
-      </c>
       <c r="G11" s="56" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H11" s="56" t="s">
         <v>186</v>
       </c>
       <c r="I11" s="56" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J11" s="56">
         <v>280</v>
@@ -4344,7 +4415,7 @@
     </row>
     <row r="12" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="56" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="56">
         <v>7</v>
@@ -4376,31 +4447,31 @@
     </row>
     <row r="13" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="56" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="56">
         <v>9</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G13" s="56" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="H13" s="56" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I13" s="56" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="J13" s="56">
         <v>410</v>
@@ -4408,7 +4479,7 @@
     </row>
     <row r="14" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A14" s="56" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B14" s="56">
         <v>9</v>
@@ -4417,22 +4488,22 @@
         <v>265</v>
       </c>
       <c r="D14" s="56" t="s">
+        <v>442</v>
+      </c>
+      <c r="E14" s="56" t="s">
         <v>443</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="F14" s="56" t="s">
         <v>444</v>
-      </c>
-      <c r="F14" s="56" t="s">
-        <v>445</v>
       </c>
       <c r="G14" s="56" t="s">
         <v>265</v>
       </c>
       <c r="H14" s="56" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I14" s="56" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J14" s="56">
         <v>549</v>
@@ -4440,31 +4511,31 @@
     </row>
     <row r="15" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A15" s="56" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B15" s="56">
         <v>9</v>
       </c>
       <c r="C15" s="56" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="56" t="s">
         <v>448</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>449</v>
       </c>
       <c r="E15" s="56" t="s">
         <v>197</v>
       </c>
       <c r="F15" s="56" t="s">
+        <v>449</v>
+      </c>
+      <c r="G15" s="56" t="s">
         <v>450</v>
-      </c>
-      <c r="G15" s="56" t="s">
-        <v>451</v>
       </c>
       <c r="H15" s="56" t="s">
         <v>186</v>
       </c>
       <c r="I15" s="56" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J15" s="56">
         <v>410</v>
@@ -4472,31 +4543,31 @@
     </row>
     <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" s="56" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B16" s="56">
         <v>6</v>
       </c>
       <c r="C16" s="48" t="s">
+        <v>690</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>691</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>692</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>693</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>690</v>
+      </c>
+      <c r="H16" s="48" t="s">
         <v>694</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>695</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>696</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>697</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>694</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>698</v>
-      </c>
       <c r="I16" s="48" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="J16" s="48">
         <v>323</v>
@@ -4504,31 +4575,31 @@
     </row>
     <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="56" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B17" s="56">
         <v>6</v>
       </c>
       <c r="C17" s="56" t="s">
+        <v>664</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>665</v>
+      </c>
+      <c r="E17" s="56" t="s">
+        <v>666</v>
+      </c>
+      <c r="F17" s="56" t="s">
+        <v>667</v>
+      </c>
+      <c r="G17" s="56" t="s">
+        <v>664</v>
+      </c>
+      <c r="H17" s="56" t="s">
         <v>668</v>
       </c>
-      <c r="D17" s="56" t="s">
-        <v>669</v>
-      </c>
-      <c r="E17" s="56" t="s">
-        <v>670</v>
-      </c>
-      <c r="F17" s="56" t="s">
-        <v>671</v>
-      </c>
-      <c r="G17" s="56" t="s">
-        <v>668</v>
-      </c>
-      <c r="H17" s="56" t="s">
-        <v>672</v>
-      </c>
       <c r="I17" s="56" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="J17" s="56">
         <v>375</v>
@@ -4536,31 +4607,31 @@
     </row>
     <row r="18" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A18" s="56" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" s="56">
         <v>6</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="F18" s="56" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="G18" s="56" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="H18" s="56" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="I18" s="56" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="J18" s="56">
         <v>379</v>
@@ -4568,31 +4639,31 @@
     </row>
     <row r="19" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="56" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B19" s="56">
         <v>7</v>
       </c>
       <c r="C19" s="56" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" s="56" t="s">
         <v>457</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="E19" s="56" t="s">
         <v>458</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="F19" s="56" t="s">
         <v>459</v>
       </c>
-      <c r="F19" s="56" t="s">
+      <c r="G19" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="I19" s="56" t="s">
         <v>460</v>
-      </c>
-      <c r="G19" s="56" t="s">
-        <v>459</v>
-      </c>
-      <c r="H19" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="I19" s="56" t="s">
-        <v>461</v>
       </c>
       <c r="J19" s="56">
         <v>398</v>
@@ -4600,31 +4671,31 @@
     </row>
     <row r="20" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="56" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B20" s="56">
         <v>9</v>
       </c>
       <c r="C20" s="56" t="s">
+        <v>462</v>
+      </c>
+      <c r="D20" s="56" t="s">
         <v>463</v>
       </c>
-      <c r="D20" s="56" t="s">
+      <c r="E20" s="56" t="s">
         <v>464</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="F20" s="56" t="s">
         <v>465</v>
       </c>
-      <c r="F20" s="56" t="s">
-        <v>466</v>
-      </c>
       <c r="G20" s="56" t="s">
+        <v>462</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="I20" s="56" t="s">
         <v>463</v>
-      </c>
-      <c r="H20" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>464</v>
       </c>
       <c r="J20" s="56">
         <v>444</v>
@@ -4632,31 +4703,31 @@
     </row>
     <row r="21" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="56" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B21" s="56">
         <v>10</v>
       </c>
       <c r="C21" s="56" t="s">
+        <v>467</v>
+      </c>
+      <c r="D21" s="56" t="s">
         <v>468</v>
       </c>
-      <c r="D21" s="56" t="s">
+      <c r="E21" s="56" t="s">
         <v>469</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="F21" s="56" t="s">
         <v>470</v>
       </c>
-      <c r="F21" s="56" t="s">
-        <v>471</v>
-      </c>
       <c r="G21" s="56" t="s">
+        <v>467</v>
+      </c>
+      <c r="H21" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="I21" s="56" t="s">
         <v>468</v>
-      </c>
-      <c r="H21" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="I21" s="56" t="s">
-        <v>469</v>
       </c>
       <c r="J21" s="56">
         <v>753</v>
@@ -4664,31 +4735,31 @@
     </row>
     <row r="22" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="56" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B22" s="56">
         <v>10</v>
       </c>
       <c r="C22" s="56" t="s">
+        <v>472</v>
+      </c>
+      <c r="D22" s="56" t="s">
         <v>473</v>
       </c>
-      <c r="D22" s="56" t="s">
+      <c r="E22" s="56" t="s">
         <v>474</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="F22" s="56" t="s">
         <v>475</v>
       </c>
-      <c r="F22" s="56" t="s">
-        <v>476</v>
-      </c>
       <c r="G22" s="56" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H22" s="56" t="s">
         <v>64</v>
       </c>
       <c r="I22" s="56" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J22" s="56">
         <v>814</v>
@@ -4696,63 +4767,63 @@
     </row>
     <row r="23" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A23" s="56" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B23" s="56">
         <v>10</v>
       </c>
       <c r="C23" s="56" t="s">
+        <v>794</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>795</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>796</v>
+      </c>
+      <c r="F23" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="D23" s="56" t="s">
+      <c r="G23" s="56" t="s">
         <v>480</v>
-      </c>
-      <c r="E23" s="56" t="s">
-        <v>481</v>
-      </c>
-      <c r="F23" s="56" t="s">
-        <v>482</v>
-      </c>
-      <c r="G23" s="56" t="s">
-        <v>483</v>
       </c>
       <c r="H23" s="56" t="s">
         <v>64</v>
       </c>
       <c r="I23" s="56" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J23" s="56">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="56" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B24" s="56">
         <v>6</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F24" s="48" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G24" s="56" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="H24" s="56" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="I24" s="56" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="J24" s="56">
         <v>344</v>
@@ -4760,31 +4831,31 @@
     </row>
     <row r="25" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A25" s="56" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B25" s="56">
         <v>6</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E25" s="56" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="F25" s="56" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G25" s="56" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="H25" s="56" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I25" s="56" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="J25" s="56">
         <v>372</v>
@@ -4792,31 +4863,31 @@
     </row>
     <row r="26" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="56" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B26" s="56">
         <v>7</v>
       </c>
       <c r="C26" s="56" t="s">
+        <v>484</v>
+      </c>
+      <c r="D26" s="56" t="s">
+        <v>485</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>486</v>
+      </c>
+      <c r="F26" s="56" t="s">
         <v>487</v>
       </c>
-      <c r="D26" s="56" t="s">
-        <v>488</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>489</v>
-      </c>
-      <c r="F26" s="56" t="s">
-        <v>490</v>
-      </c>
       <c r="G26" s="56" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H26" s="56" t="s">
         <v>64</v>
       </c>
       <c r="I26" s="56" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J26" s="56">
         <v>408</v>
@@ -4824,31 +4895,31 @@
     </row>
     <row r="27" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="56" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B27" s="56">
         <v>7</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D27" s="48" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E27" s="56" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="F27" s="56" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="G27" s="56" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="H27" s="56" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="I27" s="56" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="J27" s="56">
         <v>251</v>
@@ -4856,31 +4927,31 @@
     </row>
     <row r="28" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A28" s="56" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B28" s="56">
         <v>8</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="E28" s="56" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="F28" s="56" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G28" s="56" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="H28" s="56" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I28" s="56" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="J28" s="56">
         <v>523</v>
@@ -4888,31 +4959,31 @@
     </row>
     <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="56" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B29" s="56">
         <v>8</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F29" s="56" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G29" s="56" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="H29" s="56" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I29" s="56" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="J29" s="56">
         <v>623</v>
@@ -4920,7 +4991,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="56" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B30" s="48">
         <v>10</v>
@@ -4928,7 +4999,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="48" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B31" s="48">
         <v>6</v>
@@ -4936,7 +5007,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B32" s="48">
         <v>10</v>
@@ -4944,31 +5015,31 @@
     </row>
     <row r="33" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A33" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B33" s="48">
         <v>10</v>
       </c>
       <c r="C33" t="s">
+        <v>773</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>774</v>
+      </c>
+      <c r="E33" t="s">
         <v>777</v>
       </c>
-      <c r="D33" s="23" t="s">
-        <v>778</v>
-      </c>
-      <c r="E33" t="s">
-        <v>781</v>
-      </c>
       <c r="F33" s="23" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="G33" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="J33">
         <v>394</v>
@@ -4976,7 +5047,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="48" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B34" s="48">
         <v>10</v>
@@ -5002,13 +5073,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
@@ -5017,12 +5088,12 @@
         <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="59">
         <v>6</v>
@@ -5043,7 +5114,7 @@
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B3" s="59">
         <v>6</v>
@@ -5064,16 +5135,16 @@
     </row>
     <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" s="59">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E4" s="48">
         <v>511</v>
@@ -5085,16 +5156,16 @@
     </row>
     <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B5" s="59">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E5" s="48">
         <v>486</v>
@@ -5106,16 +5177,16 @@
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B6" s="59">
         <v>8</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E6" s="48">
         <v>501</v>
@@ -5127,16 +5198,16 @@
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" s="59">
         <v>8</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E7" s="48">
         <v>282</v>
@@ -5148,7 +5219,7 @@
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B8" s="59">
         <v>9</v>
@@ -5169,16 +5240,16 @@
     </row>
     <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B9" s="59">
         <v>6</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E9" s="48">
         <v>251</v>
@@ -5190,16 +5261,16 @@
     </row>
     <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B10" s="59">
         <v>6</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E10" s="48">
         <v>230</v>
@@ -5211,16 +5282,16 @@
     </row>
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B11" s="59">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E11" s="48">
         <v>280</v>
@@ -5232,7 +5303,7 @@
     </row>
     <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="59">
         <v>7</v>
@@ -5253,30 +5324,30 @@
     </row>
     <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="59">
         <v>9</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B14" s="59">
         <v>9</v>
       </c>
       <c r="C14" s="56" t="s">
+        <v>443</v>
+      </c>
+      <c r="D14" s="56" t="s">
         <v>444</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>445</v>
       </c>
       <c r="E14">
         <v>549</v>
@@ -5287,16 +5358,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B15" s="59">
         <v>9</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E15">
         <v>410</v>
@@ -5307,61 +5378,61 @@
     </row>
     <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B16" s="59">
         <v>6</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B17" s="59">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" s="59">
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="F18" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B19" s="59">
         <v>7</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E19">
         <v>398</v>
@@ -5372,16 +5443,16 @@
     </row>
     <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B20" s="59">
         <v>9</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E20" s="60">
         <v>444</v>
@@ -5392,16 +5463,16 @@
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B21" s="59">
         <v>10</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E21">
         <v>753</v>
@@ -5412,16 +5483,16 @@
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="62" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B22" s="59">
         <v>10</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E22">
         <v>814</v>
@@ -5432,19 +5503,19 @@
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B23" s="59">
         <v>10</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>520</v>
+        <v>797</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E23">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F23" s="60" t="s">
         <v>186</v>
@@ -5452,44 +5523,44 @@
     </row>
     <row r="24" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B24" s="48">
         <v>6</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B25" s="48">
         <v>6</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="58" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B26" s="48">
         <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E26">
         <v>408</v>
@@ -5500,49 +5571,49 @@
     </row>
     <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B27" s="48">
         <v>7</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B28" s="48">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B29" s="48">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A30" s="57" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B30" s="48">
         <v>10</v>
@@ -5550,7 +5621,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="48" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B31" s="48">
         <v>6</v>
@@ -5558,7 +5629,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B32" s="48">
         <v>10</v>
@@ -5566,21 +5637,21 @@
     </row>
     <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A33" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B33" s="48">
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="48" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B34" s="48">
         <v>10</v>
@@ -5606,7 +5677,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B1" s="59" t="s">
         <v>1</v>
@@ -5638,7 +5709,7 @@
     </row>
     <row r="2" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="59">
         <v>6</v>
@@ -5670,7 +5741,7 @@
     </row>
     <row r="3" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B3" s="59">
         <v>6</v>
@@ -5702,7 +5773,7 @@
     </row>
     <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" s="59">
         <v>7</v>
@@ -5734,7 +5805,7 @@
     </row>
     <row r="5" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B5" s="59">
         <v>8</v>
@@ -5746,10 +5817,10 @@
         <v>63</v>
       </c>
       <c r="E5" s="63" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G5" s="63" t="s">
         <v>62</v>
@@ -5767,22 +5838,22 @@
     </row>
     <row r="6" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B6" s="59">
         <v>8</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E6" s="63" t="s">
         <v>193</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G6" s="63" t="s">
         <v>193</v>
@@ -5791,7 +5862,7 @@
         <v>64</v>
       </c>
       <c r="I6" s="64" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="J6" s="63">
         <v>391</v>
@@ -5800,7 +5871,7 @@
     </row>
     <row r="7" spans="1:11" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" s="59">
         <v>7</v>
@@ -5832,7 +5903,7 @@
     </row>
     <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B8" s="59">
         <v>9</v>
@@ -5844,10 +5915,10 @@
         <v>66</v>
       </c>
       <c r="E8" s="63" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="G8" s="63" t="s">
         <v>65</v>
@@ -5865,31 +5936,31 @@
     </row>
     <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B9" s="59">
         <v>6</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H9" s="71" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="J9" s="18">
         <v>228</v>
@@ -5897,7 +5968,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B10" s="59">
         <v>6</v>
@@ -5905,31 +5976,31 @@
     </row>
     <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B11" s="59">
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="E11" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="G11" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H11" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="J11">
         <v>222</v>
@@ -5937,7 +6008,7 @@
     </row>
     <row r="12" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="59">
         <v>7</v>
@@ -5969,31 +6040,31 @@
     </row>
     <row r="13" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="59">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E13" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G13" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>64</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="J13">
         <v>398</v>
@@ -6002,31 +6073,31 @@
     </row>
     <row r="14" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B14" s="59">
         <v>8</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E14" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G14" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="H14" s="23" t="s">
         <v>64</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="J14">
         <v>490</v>
@@ -6035,31 +6106,31 @@
     </row>
     <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B15" s="59">
         <v>9</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G15" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H15" s="23" t="s">
         <v>186</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="J15">
         <v>334</v>
@@ -6068,31 +6139,31 @@
     </row>
     <row r="16" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B16" s="59">
         <v>6</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>543</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>544</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>545</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>546</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>547</v>
       </c>
       <c r="H16" s="23" t="s">
         <v>186</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="J16">
         <v>254</v>
@@ -6100,31 +6171,31 @@
     </row>
     <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B17" s="59">
         <v>6</v>
       </c>
       <c r="C17" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>547</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="H17" s="23" t="s">
         <v>549</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>550</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>551</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>552</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>549</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>553</v>
-      </c>
       <c r="I17" s="23" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="J17">
         <v>342</v>
@@ -6132,31 +6203,31 @@
     </row>
     <row r="18" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" s="59">
         <v>7</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="J18">
         <v>249</v>
@@ -6164,31 +6235,31 @@
     </row>
     <row r="19" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="61" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B19" s="59">
         <v>7</v>
       </c>
       <c r="C19" s="23" t="s">
+        <v>555</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>556</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>557</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="G19" s="23" t="s">
         <v>559</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="H19" s="23" t="s">
         <v>560</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="I19" s="23" t="s">
         <v>561</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>562</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>563</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>564</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>565</v>
       </c>
       <c r="J19">
         <v>390</v>
@@ -6196,31 +6267,31 @@
     </row>
     <row r="20" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B20" s="59">
         <v>8</v>
       </c>
       <c r="C20" s="23" t="s">
+        <v>562</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="E20" s="61" t="s">
+        <v>564</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>565</v>
+      </c>
+      <c r="G20" s="23" t="s">
         <v>566</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>567</v>
-      </c>
-      <c r="E20" s="61" t="s">
-        <v>568</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>569</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>570</v>
-      </c>
       <c r="H20" s="23" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="J20">
         <v>372</v>
@@ -6228,7 +6299,7 @@
     </row>
     <row r="21" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B21" s="59">
         <v>9</v>
@@ -6243,7 +6314,7 @@
         <v>384</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G21" t="s">
         <v>382</v>
@@ -6260,22 +6331,22 @@
     </row>
     <row r="22" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A22" s="62" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B22" s="59">
         <v>9</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E22" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G22" t="s">
         <v>311</v>
@@ -6292,7 +6363,7 @@
     </row>
     <row r="23" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B23" s="59">
         <v>10</v>
@@ -6307,7 +6378,7 @@
         <v>388</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G23" t="s">
         <v>386</v>
@@ -6324,31 +6395,31 @@
     </row>
     <row r="24" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A24" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B24" s="48">
         <v>6</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E24" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G24" t="s">
         <v>311</v>
       </c>
       <c r="H24" s="61" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J24">
         <v>314</v>
@@ -6356,31 +6427,31 @@
     </row>
     <row r="25" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A25" s="58" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B25" s="48">
         <v>7</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E25" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="H25" s="71" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="J25">
         <v>318</v>
@@ -6388,31 +6459,31 @@
     </row>
     <row r="26" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B26" s="48">
         <v>7</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H26" s="71" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="J26">
         <v>216</v>
@@ -6420,31 +6491,31 @@
     </row>
     <row r="27" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B27" s="48">
         <v>8</v>
       </c>
       <c r="C27" s="23" t="s">
+        <v>671</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>672</v>
+      </c>
+      <c r="E27" t="s">
+        <v>673</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>674</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>671</v>
+      </c>
+      <c r="H27" s="23" t="s">
         <v>675</v>
       </c>
-      <c r="D27" s="23" t="s">
-        <v>676</v>
-      </c>
-      <c r="E27" t="s">
-        <v>677</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>678</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>675</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>679</v>
-      </c>
       <c r="I27" s="23" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J27">
         <v>506</v>
@@ -6452,31 +6523,31 @@
     </row>
     <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="57" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B28" s="48">
         <v>8</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E28" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="H28" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="I28" s="23" t="s">
         <v>679</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>683</v>
       </c>
       <c r="J28">
         <v>416</v>
@@ -6484,31 +6555,31 @@
     </row>
     <row r="29" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B29" s="48">
         <v>10</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E29" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="J29">
         <v>564</v>
@@ -6516,7 +6587,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="48" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B30" s="48">
         <v>6</v>
@@ -6524,7 +6595,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B31" s="48">
         <v>10</v>
@@ -6532,18 +6603,42 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B32" s="48">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A33" s="48" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B33" s="48">
         <v>10</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>788</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>789</v>
+      </c>
+      <c r="E33" t="s">
+        <v>790</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>791</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>788</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>798</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>789</v>
+      </c>
+      <c r="J33">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -6564,13 +6659,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
@@ -6579,12 +6674,12 @@
         <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="59">
         <v>6</v>
@@ -6604,7 +6699,7 @@
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B3" s="59">
         <v>6</v>
@@ -6624,7 +6719,7 @@
     </row>
     <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" s="59">
         <v>7</v>
@@ -6644,16 +6739,16 @@
     </row>
     <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B5" s="59">
         <v>8</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="E5" s="63">
         <v>391</v>
@@ -6664,16 +6759,16 @@
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B6" s="59">
         <v>8</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E6" s="63">
         <v>391</v>
@@ -6684,7 +6779,7 @@
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" s="59">
         <v>7</v>
@@ -6704,16 +6799,16 @@
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B8" s="59">
         <v>9</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E8" s="63">
         <v>429</v>
@@ -6724,21 +6819,21 @@
     </row>
     <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B9" s="59">
         <v>6</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B10" s="59">
         <v>6</v>
@@ -6747,21 +6842,21 @@
     </row>
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B11" s="59">
         <v>6</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="59">
         <v>7</v>
@@ -6781,16 +6876,16 @@
     </row>
     <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B13" s="59">
         <v>9</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="E13">
         <v>398</v>
@@ -6802,16 +6897,16 @@
     </row>
     <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B14" s="59">
         <v>8</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E14">
         <v>490</v>
@@ -6823,16 +6918,16 @@
     </row>
     <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B15" s="59">
         <v>9</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="E15">
         <v>334</v>
@@ -6844,16 +6939,16 @@
     </row>
     <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B16" s="59">
         <v>6</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="E16">
         <v>254</v>
@@ -6864,16 +6959,16 @@
     </row>
     <row r="17" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B17" s="59">
         <v>6</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E17">
         <v>342</v>
@@ -6884,16 +6979,16 @@
     </row>
     <row r="18" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" s="59">
         <v>7</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E18">
         <v>249</v>
@@ -6904,16 +6999,16 @@
     </row>
     <row r="19" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B19" s="59">
         <v>7</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E19">
         <v>390</v>
@@ -6924,16 +7019,16 @@
     </row>
     <row r="20" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B20" s="59">
         <v>8</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="E20">
         <v>372</v>
@@ -6944,7 +7039,7 @@
     </row>
     <row r="21" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B21" s="59">
         <v>9</v>
@@ -6961,22 +7056,20 @@
       <c r="F21" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="G21" s="53" t="s">
-        <v>390</v>
-      </c>
+      <c r="G21" s="53"/>
     </row>
     <row r="22" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A22" s="62" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B22" s="59">
         <v>9</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E22">
         <v>478</v>
@@ -6984,22 +7077,20 @@
       <c r="F22" t="s">
         <v>186</v>
       </c>
-      <c r="G22" s="53" t="s">
-        <v>390</v>
-      </c>
+      <c r="G22" s="53"/>
     </row>
     <row r="23" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B23" s="59">
         <v>10</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E23">
         <v>600</v>
@@ -7007,22 +7098,20 @@
       <c r="F23" t="s">
         <v>186</v>
       </c>
-      <c r="G23" s="53" t="s">
-        <v>390</v>
-      </c>
+      <c r="G23" s="53"/>
     </row>
     <row r="24" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B24" s="48">
         <v>6</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E24">
         <v>314</v>
@@ -7033,77 +7122,77 @@
     </row>
     <row r="25" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="58" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B25" s="48">
         <v>7</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B26" s="48">
         <v>7</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B27" s="48">
         <v>8</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="57" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B28" s="48">
         <v>8</v>
       </c>
       <c r="C28" s="65" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B29" s="48">
         <v>10</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="48" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B30" s="48">
         <v>6</v>
@@ -7111,7 +7200,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B31" s="48">
         <v>10</v>
@@ -7119,18 +7208,24 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B32" s="48">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A33" s="48" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B33" s="48">
         <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>792</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -7152,7 +7247,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="65" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B1" s="59" t="s">
         <v>1</v>
@@ -7184,31 +7279,31 @@
     </row>
     <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="59">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="G2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="H2" t="s">
         <v>186</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="J2">
         <v>214</v>
@@ -7216,7 +7311,7 @@
     </row>
     <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="65" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B3" s="59">
         <v>7</v>
@@ -7248,7 +7343,7 @@
     </row>
     <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" s="65" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B4" s="59">
         <v>7</v>
@@ -7280,7 +7375,7 @@
     </row>
     <row r="5" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="65" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="59">
         <v>8</v>
@@ -7312,7 +7407,7 @@
     </row>
     <row r="6" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="65" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B6" s="59">
         <v>7</v>
@@ -7344,7 +7439,7 @@
     </row>
     <row r="7" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" s="65" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B7" s="59">
         <v>8</v>
@@ -7376,7 +7471,7 @@
     </row>
     <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="65" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B8" s="59">
         <v>6</v>
@@ -7408,7 +7503,7 @@
     </row>
     <row r="9" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="65" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B9" s="59">
         <v>6</v>
@@ -7440,7 +7535,7 @@
     </row>
     <row r="10" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="65" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="59">
         <v>6</v>
@@ -7472,31 +7567,31 @@
     </row>
     <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="65" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B11" s="59">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="E11" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="G11" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>64</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="J11">
         <v>559</v>
@@ -7505,7 +7600,7 @@
     </row>
     <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="65" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B12" s="59">
         <v>8</v>
@@ -7537,7 +7632,7 @@
     </row>
     <row r="13" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="65" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B13" s="59">
         <v>9</v>
@@ -7569,7 +7664,7 @@
     </row>
     <row r="14" spans="1:11" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A14" s="65" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B14" s="59">
         <v>6</v>
@@ -7578,13 +7673,13 @@
         <v>239</v>
       </c>
       <c r="D14" s="67" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="E14" s="66" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G14" s="54" t="s">
         <v>306</v>
@@ -7593,7 +7688,7 @@
         <v>64</v>
       </c>
       <c r="I14" s="53" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J14" s="54">
         <v>303</v>
@@ -7601,22 +7696,22 @@
     </row>
     <row r="15" spans="1:11" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A15" s="65" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B15" s="59">
         <v>6</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E15" s="55" t="s">
         <v>308</v>
       </c>
       <c r="F15" s="67" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G15" s="55" t="s">
         <v>308</v>
@@ -7625,7 +7720,7 @@
         <v>64</v>
       </c>
       <c r="I15" s="67" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="J15" s="54">
         <v>449</v>
@@ -7633,31 +7728,31 @@
     </row>
     <row r="16" spans="1:11" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A16" s="65" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B16" s="59">
         <v>8</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="D16" s="53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G16" s="66" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="H16" s="23" t="s">
         <v>64</v>
       </c>
       <c r="I16" s="53" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="J16" s="54">
         <v>406</v>
@@ -7665,31 +7760,31 @@
     </row>
     <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A17" s="65" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B17" s="59">
         <v>9</v>
       </c>
       <c r="C17" t="s">
+        <v>618</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>619</v>
+      </c>
+      <c r="E17" t="s">
+        <v>620</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>621</v>
+      </c>
+      <c r="G17" t="s">
+        <v>618</v>
+      </c>
+      <c r="H17" s="23" t="s">
         <v>622</v>
       </c>
-      <c r="D17" s="53" t="s">
-        <v>623</v>
-      </c>
-      <c r="E17" t="s">
-        <v>624</v>
-      </c>
-      <c r="F17" s="53" t="s">
-        <v>625</v>
-      </c>
-      <c r="G17" t="s">
-        <v>622</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>626</v>
-      </c>
       <c r="I17" s="53" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J17">
         <v>710</v>
@@ -7697,31 +7792,31 @@
     </row>
     <row r="18" spans="1:10" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A18" s="68" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B18" s="59">
         <v>9</v>
       </c>
       <c r="C18" s="61" t="s">
+        <v>623</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>624</v>
+      </c>
+      <c r="E18" t="s">
+        <v>625</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>626</v>
+      </c>
+      <c r="G18" t="s">
         <v>627</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="H18" s="23" t="s">
         <v>628</v>
       </c>
-      <c r="E18" t="s">
+      <c r="I18" s="53" t="s">
         <v>629</v>
-      </c>
-      <c r="F18" s="53" t="s">
-        <v>630</v>
-      </c>
-      <c r="G18" t="s">
-        <v>631</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>632</v>
-      </c>
-      <c r="I18" s="53" t="s">
-        <v>633</v>
       </c>
       <c r="J18">
         <v>654</v>
@@ -7729,31 +7824,31 @@
     </row>
     <row r="19" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="65" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B19" s="59">
         <v>10</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E19" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G19" s="61" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="J19" s="72">
         <v>842</v>
@@ -7761,31 +7856,31 @@
     </row>
     <row r="20" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="69" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B20" s="48">
         <v>6</v>
       </c>
       <c r="C20" s="61" t="s">
+        <v>761</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>762</v>
+      </c>
+      <c r="E20" t="s">
         <v>765</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="F20" s="23" t="s">
         <v>766</v>
       </c>
-      <c r="E20" t="s">
-        <v>769</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>770</v>
-      </c>
       <c r="G20" s="61" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="J20" s="72">
         <v>401</v>
@@ -7793,31 +7888,31 @@
     </row>
     <row r="21" spans="1:10" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A21" s="56" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B21" s="48">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E21" t="s">
         <v>249</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="G21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="I21" s="53" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="J21">
         <v>224</v>
@@ -7825,31 +7920,31 @@
     </row>
     <row r="22" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="56" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B22" s="48">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E22" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="G22" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J22">
         <v>589</v>
@@ -7857,51 +7952,71 @@
     </row>
     <row r="23" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A23" s="70" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B23" s="48">
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E23" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G23" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J23">
         <v>506</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A24" s="70" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B24" s="48">
         <v>9</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
+      <c r="C24" t="s">
+        <v>780</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>781</v>
+      </c>
+      <c r="E24" t="s">
+        <v>782</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>783</v>
+      </c>
+      <c r="G24" t="s">
+        <v>782</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>785</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>784</v>
+      </c>
+      <c r="J24">
+        <v>642</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B25" s="48">
         <v>10</v>
@@ -7909,7 +8024,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B26" s="48">
         <v>10</v>
@@ -7917,7 +8032,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B27" s="48">
         <v>10</v>
@@ -7943,13 +8058,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>9</v>
@@ -7958,22 +8073,22 @@
         <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G1"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B2" s="48">
         <v>6</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E2">
         <v>214</v>
@@ -7985,7 +8100,7 @@
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B3" s="59">
         <v>7</v>
@@ -8006,7 +8121,7 @@
     </row>
     <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B4" s="59">
         <v>7</v>
@@ -8027,7 +8142,7 @@
     </row>
     <row r="5" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="59">
         <v>8</v>
@@ -8048,7 +8163,7 @@
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B6" s="59">
         <v>7</v>
@@ -8069,7 +8184,7 @@
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B7" s="48">
         <v>8</v>
@@ -8090,7 +8205,7 @@
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B8" s="48">
         <v>6</v>
@@ -8111,7 +8226,7 @@
     </row>
     <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B9" s="48">
         <v>6</v>
@@ -8132,7 +8247,7 @@
     </row>
     <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="48">
         <v>6</v>
@@ -8153,16 +8268,16 @@
     </row>
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B11" s="48">
         <v>9</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E11">
         <v>559</v>
@@ -8174,7 +8289,7 @@
     </row>
     <row r="12" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B12" s="48">
         <v>8</v>
@@ -8195,7 +8310,7 @@
     </row>
     <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B13" s="48">
         <v>9</v>
@@ -8216,16 +8331,16 @@
     </row>
     <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B14" s="59">
         <v>6</v>
       </c>
       <c r="C14" s="53" t="s">
+        <v>394</v>
+      </c>
+      <c r="D14" s="53" t="s">
         <v>395</v>
-      </c>
-      <c r="D14" s="53" t="s">
-        <v>396</v>
       </c>
       <c r="E14" s="53">
         <v>303</v>
@@ -8236,16 +8351,16 @@
     </row>
     <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B15" s="59">
         <v>6</v>
       </c>
       <c r="C15" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="D15" s="53" t="s">
         <v>397</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>398</v>
       </c>
       <c r="E15" s="53">
         <v>449</v>
@@ -8256,7 +8371,7 @@
     </row>
     <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B16" s="59">
         <v>8</v>
@@ -8265,7 +8380,7 @@
         <v>357</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E16" s="53">
         <v>406</v>
@@ -8276,16 +8391,16 @@
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B17" s="59">
         <v>9</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E17" s="23">
         <v>710</v>
@@ -8296,16 +8411,16 @@
     </row>
     <row r="18" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A18" s="62" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B18" s="59">
         <v>9</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="E18" s="23">
         <v>654</v>
@@ -8316,16 +8431,16 @@
     </row>
     <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B19" s="59">
         <v>10</v>
       </c>
       <c r="C19" s="61" t="s">
+        <v>756</v>
+      </c>
+      <c r="D19" s="23" t="s">
         <v>760</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>764</v>
       </c>
       <c r="F19" s="53" t="s">
         <v>186</v>
@@ -8333,16 +8448,16 @@
     </row>
     <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="58" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B20" s="48">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="F20" s="53" t="s">
         <v>186</v>
@@ -8350,16 +8465,16 @@
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B21" s="48">
         <v>6</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D21" s="67" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E21" s="23">
         <v>224</v>
@@ -8370,16 +8485,16 @@
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B22" s="48">
         <v>8</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E22" s="23">
         <v>589</v>
@@ -8390,35 +8505,41 @@
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="57" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B23" s="48">
         <v>7</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F23" s="53" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A24" s="57" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B24" s="48">
         <v>9</v>
       </c>
+      <c r="C24" s="23" t="s">
+        <v>786</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>787</v>
+      </c>
       <c r="F24" s="53" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B25" s="48">
         <v>10</v>
@@ -8426,7 +8547,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B26" s="48">
         <v>10</v>
@@ -8434,7 +8555,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B27" s="48">
         <v>10</v>
@@ -9548,7 +9669,7 @@
     </row>
     <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="23" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B31" s="16">
         <v>9</v>
